--- a/www/download/COUNTRY.SVK.rpO1.xlsx
+++ b/www/download/COUNTRY.SVK.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>Eslováquia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>0.985998871219229</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.01726276463438</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.1157227322029</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.16924873131231</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.39161406895718</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>1.52218588940335</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>1.60446667405649</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>1.49992492877326</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>1.21805641823749</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>1.06910708892009</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>1.02787598364932</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>0.983671143712093</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>0.817768599041415</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>0.70587963903473</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.716948688620144</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2.107</t>
+          <t>1.96718949230029</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.151</t>
+          <t>1.86880095787918</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2.129</t>
+          <t>1.78783218770531</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2.119</t>
+          <t>1.77107811962931</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2.065</t>
+          <t>1.75527491892645</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>1.65621995124424</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.037</t>
+          <t>1.64365209403404</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.038</t>
+          <t>1.84924434740061</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.17352302301362</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2.056</t>
+          <t>1.81888865891484</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2.089</t>
+          <t>1.80145501502784</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2.132</t>
+          <t>1.71458416361133</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2.177</t>
+          <t>1.74813880317204</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2.262</t>
+          <t>1.70505446005293</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>1.71426138337683</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>3.76872285771846</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2.011</t>
+          <t>3.63667344931673</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.991</t>
+          <t>3.51872086945298</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.969</t>
+          <t>3.4991484707044</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>3.69481903261336</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.856</t>
+          <t>3.64043642633104</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>3.49762945535281</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.854</t>
+          <t>3.51945520228226</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>1.852</t>
+          <t>3.7050155943124</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.803</t>
+          <t>3.59948061787965</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.819</t>
+          <t>3.71206298027298</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.857</t>
+          <t>3.65186109930002</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.891</t>
+          <t>3.46721902139453</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>3.39976793819141</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>1.848</t>
+          <t>3.31770685926443</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3956.528</t>
+          <t>5.07627409048531</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3962.421</t>
+          <t>4.91030195688303</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3915.031</t>
+          <t>4.76208414176726</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3833.549</t>
+          <t>4.74687643318518</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>3735.161</t>
+          <t>4.93363423941031</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3675.511</t>
+          <t>5.095771054953</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3644.524</t>
+          <t>4.9112407052786</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3539.907</t>
+          <t>4.91985349885342</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>3463.997</t>
+          <t>2.8028710236682</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3555.952</t>
+          <t>5.13598945279718</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>3679.17</t>
+          <t>5.41055822179628</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>3728.418</t>
+          <t>5.44270897407481</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>3883.844</t>
+          <t>5.14906259226851</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>4039.07</t>
+          <t>3.94278432999498</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>3988.091</t>
+          <t>3.84949448701376</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3551.322</t>
+          <t>911215379645.226</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3557.791</t>
+          <t>932543175351.928</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3511.601</t>
+          <t>983114154590.248</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3439.541</t>
+          <t>1165113471281.42</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>3305.355</t>
+          <t>1094013992670.9</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3225.975</t>
+          <t>1252189203773.17</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3198.825</t>
+          <t>1437982124746.11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3099.35</t>
+          <t>1571416095386.42</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2995.506</t>
+          <t>2076071738970.94</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2990.358</t>
+          <t>1999484058468.16</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>3077.563</t>
+          <t>1989890213091.99</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>3106.024</t>
+          <t>2026698182552.11</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>3213.605</t>
+          <t>1962896753412.96</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>3258.575</t>
+          <t>1857453096055.45</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>3049.539</t>
+          <t>1585088434958.13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>105756875914.438</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>106304936568.784</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>116340540101.052</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>17.15</t>
+          <t>133938592088.209</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>16.89</t>
+          <t>124734235158.814</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>17.38</t>
+          <t>141722573151.666</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>151987141008.8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>16.75</t>
+          <t>169116249576.492</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>16.37</t>
+          <t>215124960559.842</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>19.21</t>
+          <t>215113809263.966</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>21.44</t>
+          <t>220157535285.476</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>22.54</t>
+          <t>217982186885.826</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>217312119298.366</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>208370601052.496</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>22.18</t>
+          <t>198574432115.603</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>713117256.916907</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>664868791.716286</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>704024773.840944</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>75.88</t>
+          <t>791155533.10815</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>77.33</t>
+          <t>837842779.434214</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>77.64</t>
+          <t>925571170.346727</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>77.87</t>
+          <t>1021037468.83211</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>79.12</t>
+          <t>958788907.771502</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>921859114.552059</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>77.11</t>
+          <t>762274695.738084</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>75.24</t>
+          <t>673160724.902436</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>74.26</t>
+          <t>567883548.492827</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>75.25</t>
+          <t>411220546.352968</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>492865454.861185</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>74.18</t>
+          <t>525058362.089176</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>15249.1093362506</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>16898.3892949043</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>18161.0896123073</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.97</t>
+          <t>18858.9196340002</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>16365.1617196085</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.98</t>
+          <t>16404.5212929492</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>16634.1031094906</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>19189.2936179011</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>26439.2844668054</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3.68</t>
+          <t>32629.9110878768</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>36548.0344549985</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>42475.1096600688</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>56067.8775486219</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.01</t>
+          <t>74068.2153629914</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>71661.2084640172</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>40965.2205264792</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>47089.4530454274</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>48600.2051358943</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>52270.1281261434</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>45750.0268185067</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10.39</t>
+          <t>46171.6237583108</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>50137.2613583073</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>10.91</t>
+          <t>57284.0131612317</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>79519.0307152261</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>92049.3539379987</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>13.36</t>
+          <t>102543.948225066</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>13.95</t>
+          <t>121148.753990753</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>156475.818475363</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>13.86</t>
+          <t>197276.085867573</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>175270.121870659</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>79.97</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>82.21</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>82.87</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>82.95</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>83.53</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>83.14</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>81.28</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>81.51</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>81.11</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>4836.19096461471</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>5701.62837290588</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6135.64293581954</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>6877.212381587</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>6487.1615341003</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>5674.46111006042</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>6.32</t>
+          <t>6827.95496708534</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>7746.74847322426</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>9881.98885097931</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>11642.6934697896</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>13410.6979202162</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>4.77</t>
+          <t>14373.2192606829</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>4.69</t>
+          <t>18748.8787394605</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>22017.7754302872</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>20919.2346228943</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.985998871219229</t>
+          <t>53722.1169427463</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.01726276463438</t>
+          <t>52867.2494734824</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.1157227322029</t>
+          <t>58432.3390913507</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.16924873131231</t>
+          <t>68030.4002114017</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.39161406895718</t>
+          <t>65645.1059447586</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.52218588940335</t>
+          <t>76345.7762792971</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.60446667405649</t>
+          <t>81794.3875739509</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.49992492877326</t>
+          <t>91209.3377179858</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1.21805641823749</t>
+          <t>116151.538065231</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>1.06910708892009</t>
+          <t>119294.399936095</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>1.02787598364932</t>
+          <t>121049.149432975</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.983671143712093</t>
+          <t>117414.529180878</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.817768599041415</t>
+          <t>114947.297671702</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.70587963903473</t>
+          <t>107796.092333083</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948688620144</t>
+          <t>107439.976342633</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>88954777721.4698</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>62170275160.5144</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>62362689865.4299</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>91124627667.6624</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>97546887603.4974</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>126508552521.919</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>127288671399.876</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>138748465786.815</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>199250668874.168</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>214778856828.198</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>202706221325.193</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>207479853280.185</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>217635015402.785</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>153415753058.813</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>93902206619.5061</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>76168293125.016</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>73961868867.0892</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>75871979645.224</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>101659127409.883</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>102458423266.721</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>140373654395.374</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>141481841853.191</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>154970403278.037</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>207062544996.373</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>192868186959.499</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>188463992204.114</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>197379731965.528</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>215785212061.221</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>164675283677.763</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>102422256217.991</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>12786484596.4539</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>-11791593706.5748</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>-13509289779.7941</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.081</t>
+          <t>-10534499742.2203</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-4911535663.22331</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>-13865101873.4559</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>-14193170453.3146</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>-16221937491.2223</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>-7811876122.20517</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>21910669868.6994</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>14242229121.0784</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>10100121314.6574</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>1849803341.56352</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>-11259530618.9505</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.271</t>
+          <t>-8520049598.4849</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>240808.187916678</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>229945.195763848</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>247594.088301842</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>286711.959765615</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>285367.798213896</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>325382.3493683</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>339220.892676609</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>383638.509495704</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>502245.04709879</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.095</t>
+          <t>500883.868495492</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>511695.702051248</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>486396.808261679</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.174</t>
+          <t>465593.937759596</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>425768.153172162</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.195</t>
+          <t>415430.794979523</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>253701.484444028</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>250945.238349106</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>285905.930357776</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>336084.936060733</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>332356.455576592</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>397897.517001931</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>426501.781328989</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>475358.34376123</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>605470.623083351</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>635117.869682012</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>646815.572656143</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>632745.568269442</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>628432.120399305</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>579107.984294913</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>559075.125208013</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>196.72</t>
+          <t>10351.6164662887</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>186.88</t>
+          <t>10209.7868203828</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>178.78</t>
+          <t>11021.2280981764</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>177.11</t>
+          <t>12467.7816367772</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>175.53</t>
+          <t>11639.4145398027</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>165.62</t>
+          <t>13620.6879779712</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>164.37</t>
+          <t>14490.7719792123</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>184.92</t>
+          <t>16402.0952439891</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>217.35</t>
+          <t>24339.5612895928</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>181.89</t>
+          <t>30296.9138541655</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>180.15</t>
+          <t>34796.8452333126</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>171.46</t>
+          <t>44573.1727259821</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>174.81</t>
+          <t>61061.8625611863</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>170.51</t>
+          <t>73507.3800417416</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>171.43</t>
+          <t>57239.2583584334</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>376.87</t>
+          <t>244629354574.921</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>363.67</t>
+          <t>240201784591.617</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>351.87</t>
+          <t>278160977485.657</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>349.91</t>
+          <t>351246228384.484</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>369.48</t>
+          <t>354030583164.406</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>364.04</t>
+          <t>456169679548.136</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>349.76</t>
+          <t>541184063893.387</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>351.95</t>
+          <t>588329731599.219</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>370.5</t>
+          <t>836466464304.302</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>359.95</t>
+          <t>845981195383.783</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>371.21</t>
+          <t>862094491443.869</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>365.19</t>
+          <t>950178582886.135</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>346.72</t>
+          <t>925821181246.815</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>339.98</t>
+          <t>834377700149.368</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>331.77</t>
+          <t>665370928210.777</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>507.63</t>
+          <t>9971.94111236904</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>491.03</t>
+          <t>12268.0238295751</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>476.21</t>
+          <t>12608.4577903186</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>474.69</t>
+          <t>14211.7350719905</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>493.36</t>
+          <t>12105.0494638383</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>509.58</t>
+          <t>13679.5757818173</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>491.12</t>
+          <t>15893.3534296949</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>491.99</t>
+          <t>17703.8140097263</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>280.29</t>
+          <t>24067.1026816729</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>513.6</t>
+          <t>30326.5043170794</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>541.06</t>
+          <t>35572.909817733</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>544.27</t>
+          <t>45020.0498790437</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>514.91</t>
+          <t>59368.9390783811</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>394.28</t>
+          <t>72874.1417025702</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>384.95</t>
+          <t>55238.9468660171</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>534598.246</t>
+          <t>319727142161.314</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>539811.815</t>
+          <t>369356960238.995</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>608666.851</t>
+          <t>393434982853.853</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>712121.633</t>
+          <t>507771386307.479</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>686376.902</t>
+          <t>470378503474.133</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>805680.002</t>
+          <t>585357829794.421</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>868576.422</t>
+          <t>737104578134.983</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>968977.103</t>
+          <t>788487082777.987</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>1247553.449</t>
+          <t>1023610006895.57</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>1305628.953</t>
+          <t>1061838610002.59</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>1351141.458</t>
+          <t>1089948162793.35</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>1349259.69</t>
+          <t>1170003869306.94</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>1368078.502</t>
+          <t>1109021123999.78</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>1310112.423</t>
+          <t>978272981314.153</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1258579.647</t>
+          <t>729680890030.482</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>474052.831</t>
+          <t>379.675353919671</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>462371.5</t>
+          <t>-2058.23700919231</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>492967.258</t>
+          <t>-1587.22969214215</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>564479.94</t>
+          <t>-1743.95343521331</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>542235.914</t>
+          <t>-465.634924035594</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>604015.39</t>
+          <t>-58.8878038461029</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>630327.033</t>
+          <t>-1402.58145048259</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>711325.261</t>
+          <t>-1301.71876573727</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>930211.065</t>
+          <t>272.458607919924</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>903202.808</t>
+          <t>-29.5904629139157</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>930644</t>
+          <t>-776.064584420391</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>903004.43</t>
+          <t>-446.877153061536</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>880222.566</t>
+          <t>1692.92348280518</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>823012.82</t>
+          <t>633.238339171445</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>767814.151</t>
+          <t>2000.31149241636</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>911215.38</t>
+          <t>-75097787586.3936</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>932543.175</t>
+          <t>-129155175647.378</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>983114.155</t>
+          <t>-115274005368.196</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1165113.471</t>
+          <t>-156525157922.996</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>1094013.993</t>
+          <t>-116347920309.728</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1252189.204</t>
+          <t>-129188150246.285</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1437982.125</t>
+          <t>-195920514241.596</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1571416.095</t>
+          <t>-200157351178.767</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2076071.739</t>
+          <t>-187143542591.268</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1999484.058</t>
+          <t>-215857414618.805</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>1989890.213</t>
+          <t>-227853671349.482</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026698.183</t>
+          <t>-219825286420.801</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>1962896.753</t>
+          <t>-183199942752.963</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>1857453.096</t>
+          <t>-143895281164.785</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>1585088.435</t>
+          <t>-64309961819.7052</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>9949.73537</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>11076.07584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>10484.77652</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>10822.72855</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>9856.07718</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>9877.84729</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>10295.9501</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>11708.89663</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>15736.3511</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>19759.02915</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>22007.46628</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>26347.03686</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>35727.13067</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.197</t>
+          <t>45312.27975</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>39378.88229</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>339195.61</t>
+          <t>0.090748847984198</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>334649.833</t>
+          <t>0.0792387016025794</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>367373.434</t>
+          <t>0.0700384931463449</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>420369.762</t>
+          <t>0.0618776921599689</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>391337.823</t>
+          <t>0.0597925803915121</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>444895.864</t>
+          <t>0.0701091127758251</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>477081.162</t>
+          <t>0.0626623839208485</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>526401.053</t>
+          <t>0.0654072210007268</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>690273.143</t>
+          <t>0.0725551337240385</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>708782.672</t>
+          <t>0.0832771275182665</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>709223.483</t>
+          <t>0.0805325673570078</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>710566.347</t>
+          <t>0.0972976531718734</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>703338.419</t>
+          <t>0.104835879881524</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>697389.323</t>
+          <t>0.113964217768146</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>648081.667</t>
+          <t>0.0994072733229005</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>5894.25037387876</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>6603.75080997851</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>7040.07879467815</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>7300.48399943145</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>6386.01976775629</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>6408.69031067664</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>6434.05720682011</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>7438.84156967545</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>9969.87089404469</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>12063.8341282007</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>13882.2527629599</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>16059.1275751979</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>21385.5337672559</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>27426.80672863</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>26902.3427813828</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>105756.876</t>
+          <t>6561.3869648896</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>106304.937</t>
+          <t>7312.97872018727</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>116340.54</t>
+          <t>7842.89355693317</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>133938.592</t>
+          <t>8135.20634611494</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>124734.235</t>
+          <t>7210.15848883682</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>141722.573</t>
+          <t>7311.75335210429</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>151987.141</t>
+          <t>7333.6971430638</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>169116.25</t>
+          <t>8486.40175983047</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>215124.961</t>
+          <t>11434.3765778881</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>215113.809</t>
+          <t>14226.8452442885</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>220157.535</t>
+          <t>16425.3731892327</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>217982.187</t>
+          <t>19014.5350364168</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>217312.119</t>
+          <t>25613.2077510367</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>208370.601</t>
+          <t>32694.8229586497</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>198574.432</t>
+          <t>32072.4831027948</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>67974.0340237687</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>76089.0821652557</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>76225.1820023043</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>81488.688512532</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>74666.3660914128</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>75271.0594799448</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>78839.4587108452</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>90809.7029054219</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>117715.378261412</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>142386.934915846</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>158701.616501227</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>176099.21354047</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>224127.269080553</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>275751.31612799</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>271426.315121503</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>713.117</t>
+          <t>6561.3869648896</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>664.869</t>
+          <t>7158.20272882798</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>704.025</t>
+          <t>8026.97714936827</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>791.156</t>
+          <t>8181.77592911671</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>837.843</t>
+          <t>8034.51778925982</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>925.571</t>
+          <t>8183.77548044168</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1021.037</t>
+          <t>8343.3197503356</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>958.789</t>
+          <t>8763.44569555475</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>921.859</t>
+          <t>9272.62748129977</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>762.275</t>
+          <t>9618.57064797771</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>673.161</t>
+          <t>10696.1554796788</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>567.884</t>
+          <t>11674.1399216049</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>411.221</t>
+          <t>13244.8694598298</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>492.865</t>
+          <t>14285.14497636</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>525.058</t>
+          <t>14160.5412041467</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5894.25037387876</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>6470.7072546478</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>7225.14170477271</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>7350.23570289687</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>7135.50794459346</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>7169.05179711589</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>7301.24692839786</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>7657.1766798517</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>8069.40186823319</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>8205.66423332557</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>9107.20554338702</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>9937.39322600055</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>11190.8437912736</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>12162.7748933266</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>12015.158418251</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>11004.7562451104</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>11730.8284498127</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>11474.3398230668</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>11919.5443638851</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>10951.6562311632</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>10951.6483078957</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>11768.2233969362</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>13686.3587801695</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>18422.8438621119</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>23500.2684057115</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>26191.3465407673</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>31507.2594635832</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>42245.4581989633</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>53443.5584713503</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>47900.9845172052</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>474052831459.081</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>462371500189.989</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>492967257631.617</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>564479939946.342</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>542235914420.17</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>604015389691.11</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>630327033156.86</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>711325260574.008</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>930211065201.952</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>903202807580.705</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>930643999627.196</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>903004429680.355</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>880222566310.213</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>823012820458.861</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>767814150789.774</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>534598245811.55</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>539811815446.099</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>608666850574.252</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>712121632810.749</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>686376901997.033</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>805680002018.74</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>868576422199.643</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>968977102939.703</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1247553449273.93</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1305628952887.79</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>1351141458323.86</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>1349259689576.51</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>1368078501577.8</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>1310112423044.78</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1258579647201.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>339195609702.663</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>334649833290.711</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>367373434139.161</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>420369761986.435</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>391337823354.708</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>444895864256.9</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>477081162484.911</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>526401053037.138</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>690273143251.959</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>708782672102.06</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>709223482502.625</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>710566346875.787</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>703338419209.315</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>697389322888.55</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>648081667081.062</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2107194</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2151114</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2128906</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2118874</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2065183</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2024843</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2036513</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2038414</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>2060469</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>2055727</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2088913</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>2132389</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2176971</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>2262293.83564775</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>2251181.62202833</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1968591</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2010790</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1991030</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1968805</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1900130</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1856325</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1858161</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>1854155</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>1852106</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1803218</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>1818745</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>1856518</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>1890537</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>1933007</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1848236</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>3956528000</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>3962421000</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>3915031000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>3833549000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>3735161000</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>3675511000</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>3644524000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>3539907000</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>3463997000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3555952000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>3679170000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>3728418000</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>3883844000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>4039070106.46838</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>3988090533.37074</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3551322000</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>3557791000</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>3511601000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>3439541000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>3305355000</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3225975000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>3198825000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>3099350000</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>2995506000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>2990358000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>3077563000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>3106024000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>3213605000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>3258575000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3049539000</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.171483143334509</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.168935470315182</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.1738213275488</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.17480836933318</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.167515496055335</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.163708469360586</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.192073523559564</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.214433707344593</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.225375204233753</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.215318684569931</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.213480703104851</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.221841624622938</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.758796601193078</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.773284567686399</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.776372324109149</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.778684350268195</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.791171388899219</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.773020074994206</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.771119572719882</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.752394254379362</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.742645730092074</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.752520864796886</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.746381587509367</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.741808409964212</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.0697202554724135</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.0577799619984186</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.0498063483420509</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.0465072803986258</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.041313115045446</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.0632714556452081</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0368069037205545</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.0331720382760451</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.0319790656741731</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.0321604506331831</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0401377093857823</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.03634996541285</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.10880632060207</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.10880632060207</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.10880632060207</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.10880632060207</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.102932231374819</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.103885773438721</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.107318689593067</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.109055839789039</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.115067432691534</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.121046962340549</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.1335667069695</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.139539346363986</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.137991242044482</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.138555441233436</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.146646103261557</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.799744870939769</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.799744870939769</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.799744870939769</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.799744870939769</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.822078293684542</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.828733400228587</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.829467437184487</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.835307999257341</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.831442319362502</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.82708466204088</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.818013188934133</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.812790311137944</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.81512106377372</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.813971932958152</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.811104377949596</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.0914488084581614</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.0914488084581614</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.0914488084581614</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.0914488084581614</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.0749894749406389</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.0673808263326924</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.0632138732224457</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.0556361609536206</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.0534902479459647</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.0518683756185707</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.0484201040963663</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.0476703424980709</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.0468876941817977</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.0474726258084123</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.0422495187888463</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>45337.56892</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>50111.26536</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>50817.40235</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>53365.72453</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>47079.18453</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>49218.95513</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>50782.82322</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>58743.00054</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>79164.32126</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>95242.26689</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>107692.82259</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>129809.86542</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>173989.93873</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>222263.09264</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>195303.18255</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>17566.14321</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>19043.80717</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>19317.23338</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>20054.75071</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>18161.81472</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>18263.40166</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>19101.92054</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>22172.76054</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>29857.22044</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>37727.11365</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>42616.71973</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>50521.7945</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>67858.66595</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>86138.38143</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>79973.46762</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>67022.318965815</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>70576.7592205476</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>74696.0349082144</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>79173.1173978165</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>82159.6337902655</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>84351.6781676676</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>87222.5676832304</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>89935.468029979</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>92321.2550077123</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>94910.7692812392</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>98548.0384099257</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>102713.035738512</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>107404.941944248</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>111919.701274916</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>114233.403024763</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
